--- a/GameConfig/Datas/skilllevel.xlsx
+++ b/GameConfig/Datas/skilllevel.xlsx
@@ -1,65 +1,174 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7be9ddd9b40c4127"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\FreshGuard\GameConfig\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB7FE36-E406-4C0B-8928-86793B126381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="43200" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>skillId</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>intValues</t>
+  </si>
+  <si>
+    <t>floatValues</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>int#ref=skill.TbSkill</t>
+  </si>
+  <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>(array#sep=,),float</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>等级记录唯一ID</t>
+  </si>
+  <si>
+    <t>所属技能ID，引用skill表</t>
+  </si>
+  <si>
+    <t>技能等级，从1开始；同技能不得重复</t>
+  </si>
+  <si>
+    <t>1505：第1项=直接伤害；多项用逗号分隔</t>
+  </si>
+  <si>
+    <t>1505：第1项=减速比例0~1，第2项=持续秒数；用逗号分隔</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>0.3,3</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE7EEF8"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border/>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="5">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7EEF8"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -250,130 +359,133 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="21" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="29" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="21" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="39" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="39" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="3" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="str">
-        <x:v>skillId</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="str">
-        <x:v>level</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="str">
-        <x:v>intValues</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="str">
-        <x:v>floatValues</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="2" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B2" s="2"/>
-      <x:c r="C2" s="2"/>
-      <x:c r="D2" s="2"/>
-      <x:c r="E2" s="2"/>
-      <x:c r="F2" s="2"/>
-    </x:row>
-    <x:row r="3" ht="26" customHeight="1">
-      <x:c r="A3" s="2" t="str">
-        <x:v>##type</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="str">
-        <x:v>int#ref=skill.TbSkill</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="str">
-        <x:v>(array#sep=,),int</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="str">
-        <x:v>(array#sep=,),float</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="26" customHeight="1">
-      <x:c r="A4" s="2" t="str">
-        <x:v>##group</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="str">
-        <x:v>c</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="70" customHeight="1">
-      <x:c r="A5" s="4" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="str">
-        <x:v>等级记录唯一ID</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="str">
-        <x:v>所属技能ID，引用skill表</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="str">
-        <x:v>技能等级，从1开始；同技能不得重复</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="str">
-        <x:v>1505：第1项=直接伤害；多项用逗号分隔</x:v>
-      </x:c>
-      <x:c r="F5" s="4" t="str">
-        <x:v>1505：第1项=减速比例0~1，第2项=持续秒数；用逗号分隔</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="1"/>
-      <x:c r="B6" s="1" t="n">
-        <x:v>150501</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="n">
-        <x:v>1505</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="str">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="str">
-        <x:v>0.3,3</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="39" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="26.1" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="26.1" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" ht="26.1" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="26.1" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="33">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="26.1" customHeight="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
+        <v>150501</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1505</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>